--- a/applications/LL311_BLE/doc/pin_assignment.xlsx
+++ b/applications/LL311_BLE/doc/pin_assignment.xlsx
@@ -468,13 +468,16 @@
     <t>P1.14</t>
   </si>
   <si>
-    <t>VBATT_NTC</t>
-  </si>
-  <si>
-    <t>电池温度检测</t>
-  </si>
-  <si>
-    <t>只在充电的时候硬线路才会使能，才需要去监测ADC</t>
+    <t>NFC_NPD</t>
+  </si>
+  <si>
+    <t>NFC模块硬件复位信号</t>
+  </si>
+  <si>
+    <t>默认低电平（关断）</t>
+  </si>
+  <si>
+    <t>NFC模块上电后</t>
   </si>
   <si>
     <t>P2.00</t>
@@ -508,9 +511,6 @@
   </si>
   <si>
     <t>4G模块电源控制信号</t>
-  </si>
-  <si>
-    <t>默认低电平（关断）</t>
   </si>
   <si>
     <t>关闭输入缓冲</t>
@@ -2449,10 +2449,10 @@
         <v>123</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>118</v>
+        <v>57</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>12</v>
@@ -2461,80 +2461,80 @@
         <v>32</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:8">
       <c r="A24" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:8">
       <c r="A25" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:8">
       <c r="A26" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>137</v>
@@ -2554,13 +2554,13 @@
         <v>57</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>137</v>
@@ -2580,13 +2580,13 @@
         <v>57</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>137</v>
@@ -2606,13 +2606,13 @@
         <v>57</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>137</v>
@@ -2632,13 +2632,13 @@
         <v>57</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>137</v>
@@ -2664,7 +2664,7 @@
         <v>15</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>154</v>
@@ -2690,7 +2690,7 @@
         <v>15</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>154</v>
@@ -2716,7 +2716,7 @@
         <v>15</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>154</v>
@@ -2742,7 +2742,7 @@
         <v>15</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>154</v>
@@ -2765,10 +2765,10 @@
         <v>163</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H35" s="9" t="s">
         <v>164</v>

--- a/applications/LL311_BLE/doc/pin_assignment.xlsx
+++ b/applications/LL311_BLE/doc/pin_assignment.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="168">
   <si>
     <t>nRF54L15 MCU硬件引脚功能需遵循以下整体特性</t>
   </si>
@@ -399,7 +399,7 @@
     <t>FUN_KEY</t>
   </si>
   <si>
-    <t>功能按钮</t>
+    <t>功能按钮，低电平有效</t>
   </si>
   <si>
     <t>内部上拉，双沿触发</t>
@@ -411,10 +411,13 @@
     <t>P1.10</t>
   </si>
   <si>
-    <t>CDS_DET</t>
-  </si>
-  <si>
-    <t>光感检测（IO信号）</t>
+    <t>LIGHT_SENSOR_DET</t>
+  </si>
+  <si>
+    <t>光感检测（IO信号），有光时高电平，无光时低电平</t>
+  </si>
+  <si>
+    <t>外部1M电阻下拉，双沿触发，</t>
   </si>
   <si>
     <t>避免中间电平，防频繁唤醒</t>
@@ -426,7 +429,10 @@
     <t>LOCK_LINE_DET</t>
   </si>
   <si>
-    <t>剪线检测</t>
+    <t>锁销检测（IO信号），插入为高电平，断开时为低电平</t>
+  </si>
+  <si>
+    <t>外部1M电阻下拉，双沿触发</t>
   </si>
   <si>
     <t>P1.12</t>
@@ -2348,7 +2354,7 @@
         <v>51</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>12</v>
@@ -2357,24 +2363,24 @@
         <v>32</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:8">
       <c r="A20" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>12</v>
@@ -2383,24 +2389,24 @@
         <v>32</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:8">
       <c r="A21" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>12</v>
@@ -2409,24 +2415,24 @@
         <v>32</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:8">
       <c r="A22" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>12</v>
@@ -2435,24 +2441,24 @@
         <v>32</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:8">
       <c r="A23" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>12</v>
@@ -2461,322 +2467,322 @@
         <v>32</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:8">
       <c r="A24" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:8">
       <c r="A25" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:8">
       <c r="A26" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:8">
       <c r="A27" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:8">
       <c r="A28" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:8">
       <c r="A29" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:8">
       <c r="A30" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:8">
       <c r="A31" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:8">
       <c r="A32" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:8">
       <c r="A33" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:8">
       <c r="A34" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:8">
       <c r="A35" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:8">
       <c r="A36" s="9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
